--- a/sources/kazuya_step3.xlsx
+++ b/sources/kazuya_step3.xlsx
@@ -690,6 +690,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>06b27057-ba76-403e-85c6-5241d4d27973</t>
@@ -722,6 +727,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>22c62dd3-2f75-4092-bad9-4baa879dd867</t>
@@ -759,6 +769,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>5693325a-9d43-4c1e-9f0a-37293eb4860d</t>
@@ -801,6 +816,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>d51fee9f-9d4e-4225-aa39-2f2d2e364398</t>
@@ -838,6 +858,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>9463b80f-225a-4a7a-b350-0a3008c72604</t>
@@ -873,6 +898,11 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>cc572ca8-7e2b-4695-be36-969d95d53b5c</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4236,6 +4266,11 @@
           <t>hh"hh"mm"Lhmm</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>a1af16e4-84f3-4abd-b887-4c65bc756223</t>
@@ -4263,6 +4298,11 @@
           <t>hh'hh"mm"LL"m!</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>1abe1117-e220-4cde-b7c9-6a59e7c16e8d</t>
@@ -4288,6 +4328,11 @@
       <c r="I83" t="inlineStr">
         <is>
           <t>hh"mm"sm"L"m!</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ca41b863-8414-4a05-af5c-d5d050d26435</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
